--- a/fase1/data/output/Hand_in_sheet_part1.xlsx
+++ b/fase1/data/output/Hand_in_sheet_part1.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D2" s="11" t="n"/>
